--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260609.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260609.xlsx
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>117,689,465</t>
+          <t>159,161,179</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>159,161,179</t>
+          <t>117,689,465</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
